--- a/Releve_materiel_equipe.xlsx
+++ b/Releve_materiel_equipe.xlsx
@@ -16,7 +16,6 @@
     <sheet name="Relevé équipe" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
